--- a/cfg/excel/__enums__.xlsx
+++ b/cfg/excel/__enums__.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\AppData\Local\Kingsoft\WPSOFF~1\1210~1.291\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowWidth="31230" windowHeight="15135"/>
   </bookViews>
   <sheets>
-    <sheet name="enums" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="249">
   <si>
     <t>##var</t>
   </si>
@@ -55,7 +55,7 @@
     <t>tags</t>
   </si>
   <si>
-    <t>items</t>
+    <t>*items</t>
   </si>
   <si>
     <t>name</t>
@@ -67,55 +67,709 @@
     <t>value</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
+    <t>全名(包含模块和名字)</t>
+  </si>
+  <si>
+    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+  </si>
+  <si>
+    <t>枚举项是否唯一</t>
+  </si>
+  <si>
     <t>枚举名</t>
   </si>
   <si>
-    <t>唯一值</t>
-  </si>
-  <si>
-    <t>分组</t>
+    <t>别名</t>
+  </si>
+  <si>
+    <t>值</t>
   </si>
   <si>
     <t>注释</t>
   </si>
   <si>
-    <t>枚举项</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
+    <t>DamageHitType</t>
+  </si>
+  <si>
+    <t>Hit</t>
+  </si>
+  <si>
+    <t>普通受击</t>
+  </si>
+  <si>
+    <t>HitBack</t>
+  </si>
+  <si>
+    <t>击退</t>
+  </si>
+  <si>
+    <t>HitDown</t>
+  </si>
+  <si>
+    <t>击倒</t>
+  </si>
+  <si>
+    <t>HitFly</t>
+  </si>
+  <si>
+    <t>击飞</t>
+  </si>
+  <si>
+    <t>CursorType</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通光标</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>选择</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>UI光标</t>
+  </si>
+  <si>
+    <t>TargetSelectType</t>
+  </si>
+  <si>
+    <t>Caster</t>
+  </si>
+  <si>
+    <t>技能释放者</t>
+  </si>
+  <si>
+    <t>LabelText("技能释放者")</t>
+  </si>
+  <si>
+    <t>MainTarget</t>
+  </si>
+  <si>
+    <t>技能主目标</t>
+  </si>
+  <si>
+    <t>LabelText("技能主目标")</t>
+  </si>
+  <si>
+    <t>TargetList</t>
+  </si>
+  <si>
+    <t>所有目标列表</t>
+  </si>
+  <si>
+    <t>LabelText("所有目标列表")</t>
+  </si>
+  <si>
+    <t>HatedList</t>
+  </si>
+  <si>
+    <t>仇恨列表</t>
+  </si>
+  <si>
+    <t>LabelText("仇恨列表")</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>来源对象</t>
+  </si>
+  <si>
+    <t>LabelText("来源对象")</t>
+  </si>
+  <si>
+    <t>Empty</t>
+  </si>
+  <si>
+    <t>空对象</t>
+  </si>
+  <si>
+    <t>LabelText("空对象")</t>
+  </si>
+  <si>
+    <t>TargetListFriendly</t>
+  </si>
+  <si>
+    <t>所有目标中的友方</t>
+  </si>
+  <si>
+    <t>LabelText("所有目标中的友方")</t>
+  </si>
+  <si>
+    <t>TargetListEnemy</t>
+  </si>
+  <si>
+    <t>所有目标中的敌方</t>
+  </si>
+  <si>
+    <t>LabelText("所有目标中的敌方")</t>
+  </si>
+  <si>
+    <t>Summon</t>
+  </si>
+  <si>
+    <t>召唤物</t>
+  </si>
+  <si>
+    <t>LabelText("召唤物")</t>
+  </si>
+  <si>
+    <t>TargetSortType</t>
+  </si>
+  <si>
+    <t>Serializable, ActionName("目标优先级")</t>
+  </si>
+  <si>
+    <t>DistanceMin</t>
+  </si>
+  <si>
+    <t>由近到远排序</t>
+  </si>
+  <si>
+    <t>LabelText("由近到远排序")</t>
+  </si>
+  <si>
+    <t>DistanceMax</t>
+  </si>
+  <si>
+    <t>由远到近排序</t>
+  </si>
+  <si>
+    <t>LabelText("由远到近排序")</t>
+  </si>
+  <si>
+    <t>无排序</t>
+  </si>
+  <si>
+    <t>LabelText("无排序")</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>随机排序</t>
+  </si>
+  <si>
+    <t>LabelText("随机排序")</t>
+  </si>
+  <si>
+    <t>Hate</t>
+  </si>
+  <si>
+    <t>仇恨值排序</t>
+  </si>
+  <si>
+    <t>LabelText("仇恨值排序")</t>
+  </si>
+  <si>
+    <t>CreateTime</t>
+  </si>
+  <si>
+    <t>创建时间排序</t>
+  </si>
+  <si>
+    <t>LabelText("创建时间排序")</t>
+  </si>
+  <si>
+    <t>Atrribute</t>
+  </si>
+  <si>
+    <t>属性排序</t>
+  </si>
+  <si>
+    <t>LabelText("属性排序")</t>
+  </si>
+  <si>
+    <t>主目标排序</t>
+  </si>
+  <si>
+    <t>LabelText("主目标排序")</t>
+  </si>
+  <si>
+    <t>TargetFilterType</t>
+  </si>
+  <si>
+    <t>Serializable, ActionName("目标过滤器")</t>
+  </si>
+  <si>
+    <t>FoeFilter</t>
+  </si>
+  <si>
+    <t>敌方阵营</t>
+  </si>
+  <si>
+    <t>LabelText("敌方阵营")</t>
+  </si>
+  <si>
+    <t>OwnFilter</t>
+  </si>
+  <si>
+    <t>友方阵营</t>
+  </si>
+  <si>
+    <t>LabelText("友方阵营")</t>
+  </si>
+  <si>
+    <t>OwnOrFoeFilter</t>
+  </si>
+  <si>
+    <t>敌方阵营或友方阵营</t>
+  </si>
+  <si>
+    <t>LabelText("敌方阵营或友方阵营")</t>
+  </si>
+  <si>
+    <t>NotSelf</t>
+  </si>
+  <si>
+    <t>非自己</t>
+  </si>
+  <si>
+    <t>LabelText("非自己")</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>英雄单位</t>
+  </si>
+  <si>
+    <t>LabelText("英雄单位")</t>
+  </si>
+  <si>
+    <t>NPC</t>
+  </si>
+  <si>
+    <t>NPC单位</t>
+  </si>
+  <si>
+    <t>LabelText("NPC单位")</t>
+  </si>
+  <si>
+    <t>ClipType</t>
+  </si>
+  <si>
+    <t>Serializable</t>
+  </si>
+  <si>
+    <t>Anim</t>
+  </si>
+  <si>
+    <t>Ctrl</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Missile</t>
+  </si>
+  <si>
+    <t>EffectBindType</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LabelText("不绑定")</t>
+  </si>
+  <si>
+    <t>Bind</t>
+  </si>
+  <si>
+    <t>LabelText("绑定")</t>
+  </si>
+  <si>
+    <t>Follow</t>
+  </si>
+  <si>
+    <t>LabelText("跟随")</t>
+  </si>
+  <si>
+    <t>EffectSyncType</t>
+  </si>
+  <si>
+    <t>SyncPos</t>
+  </si>
+  <si>
+    <t>LabelText("只同步位置")</t>
+  </si>
+  <si>
+    <t>SyncRot</t>
+  </si>
+  <si>
+    <t>LabelText("只同步旋转")</t>
+  </si>
+  <si>
+    <t>SyncPosAndRot</t>
+  </si>
+  <si>
+    <t>LabelText("同步位置跟旋转")</t>
+  </si>
+  <si>
+    <t>CtrlType</t>
+  </si>
+  <si>
+    <t>PreShake</t>
+  </si>
+  <si>
+    <t>LabelText("前摇")</t>
+  </si>
+  <si>
+    <t>AfterShake</t>
+  </si>
+  <si>
+    <t>LabelText("后摇")</t>
+  </si>
+  <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>LabelText("连招")</t>
+  </si>
+  <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>LabelText("低伤害")</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>LabelText("中伤害")</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>LabelText("高伤害")</t>
+  </si>
+  <si>
+    <t>VeryHigh</t>
+  </si>
+  <si>
+    <t>LabelText("超高伤害")</t>
+  </si>
+  <si>
+    <t>SkillType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>LabelText("普通技能")</t>
+  </si>
+  <si>
+    <t>SkillMove</t>
+  </si>
+  <si>
+    <t>LabelText("跑技能")</t>
+  </si>
+  <si>
+    <t>SkillJump</t>
+  </si>
+  <si>
+    <t>LabelText("跳技能")</t>
+  </si>
+  <si>
+    <t>SkillCharge</t>
+  </si>
+  <si>
+    <t>LabelText("充能技能")</t>
+  </si>
+  <si>
+    <t>SkillTurnType</t>
+  </si>
+  <si>
+    <t>TurnToMainTarget</t>
+  </si>
+  <si>
+    <t>LabelText("看向主目标")</t>
+  </si>
+  <si>
+    <t>FollowMainTarget</t>
+  </si>
+  <si>
+    <t>LabelText("跟随主目标")</t>
+  </si>
+  <si>
+    <t>TurnToSummoner</t>
+  </si>
+  <si>
+    <t>LabelText("看向主人")</t>
+  </si>
+  <si>
+    <t>FollowSummoner</t>
+  </si>
+  <si>
+    <t>LabelText("跟随主人")</t>
+  </si>
+  <si>
+    <t>MissileShootType</t>
+  </si>
+  <si>
+    <t>FindTarget</t>
+  </si>
+  <si>
+    <t>LabelText("索敌")</t>
+  </si>
+  <si>
+    <t>FindTargetAndBlock</t>
+  </si>
+  <si>
+    <t>LabelText("索敌并且碰撞")</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>LabelText("碰撞")</t>
+  </si>
+  <si>
+    <t>AlwaysBlock</t>
+  </si>
+  <si>
+    <t>LabelText("总是碰撞")</t>
+  </si>
+  <si>
+    <t>MissileType</t>
+  </si>
+  <si>
+    <t>LabelText("普通")</t>
+  </si>
+  <si>
+    <t>Catapult</t>
+  </si>
+  <si>
+    <t>LabelText("弹射")</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>LabelText("分裂")</t>
+  </si>
+  <si>
+    <t>SnapShoot</t>
+  </si>
+  <si>
+    <t>LabelText("闪射")</t>
+  </si>
+  <si>
+    <t>MoveType</t>
+  </si>
+  <si>
+    <t>BaseSpeed</t>
+  </si>
+  <si>
+    <t>LabelText("基于速度")</t>
+  </si>
+  <si>
+    <t>BaseTime</t>
+  </si>
+  <si>
+    <t>LabelText("基于时间")</t>
+  </si>
+  <si>
+    <t>HitType</t>
+  </si>
+  <si>
+    <t>Serializable, ActionName("受击类型")</t>
+  </si>
+  <si>
+    <t>LabelText("普通受击")</t>
+  </si>
+  <si>
+    <t>LabelText("击退")</t>
+  </si>
+  <si>
+    <t>LabelText("击倒")</t>
+  </si>
+  <si>
+    <t>LabelText("击飞")</t>
+  </si>
+  <si>
+    <t>HitStun</t>
+  </si>
+  <si>
+    <t>LabelText("击晕")</t>
+  </si>
+  <si>
+    <t>EntityType</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>LabelText("怪物")</t>
+  </si>
+  <si>
+    <t>Npc</t>
+  </si>
+  <si>
+    <t>LabelText("Npc")</t>
+  </si>
+  <si>
+    <t>AirWall</t>
+  </si>
+  <si>
+    <t>LabelText("空气墙")</t>
+  </si>
+  <si>
+    <t>RangeType</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>LabelText("圆形")</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>LabelText("矩形")</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>LabelText("剧情事件")</t>
+  </si>
+  <si>
+    <t>CollectionType</t>
+  </si>
+  <si>
+    <t>Ammo</t>
+  </si>
+  <si>
+    <t>LabelText("弹药")</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>LabelText("血包")</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>LabelText("护甲")</t>
+  </si>
+  <si>
+    <t>BodyArmor</t>
+  </si>
+  <si>
+    <t>LabelText("防弹衣")</t>
   </si>
   <si>
     <t>ItemType</t>
   </si>
   <si>
-    <t>道具类型</t>
-  </si>
-  <si>
-    <t>Currency;Prop</t>
-  </si>
-  <si>
-    <t>1;2</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>LabelText("货币")</t>
+  </si>
+  <si>
+    <t>Prop</t>
+  </si>
+  <si>
+    <t>LabelText("道具")</t>
+  </si>
+  <si>
+    <t>JobType</t>
+  </si>
+  <si>
+    <t>BreakThrough</t>
+  </si>
+  <si>
+    <t>LabelText("突破")</t>
+  </si>
+  <si>
+    <t>Infantry</t>
+  </si>
+  <si>
+    <t>LabelText("步兵")</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>LabelText("重装")</t>
+  </si>
+  <si>
+    <t>Snip</t>
+  </si>
+  <si>
+    <t>LabelText("狙击")</t>
+  </si>
+  <si>
+    <t>Investigate</t>
+  </si>
+  <si>
+    <t>LabelText("侦查")</t>
+  </si>
+  <si>
+    <t>rarityType</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>LabelText("N")</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>LabelText("R")</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>LabelText("SR")</t>
+  </si>
+  <si>
+    <t>UR</t>
+  </si>
+  <si>
+    <t>LabelText("UR")</t>
+  </si>
+  <si>
+    <t>SER</t>
+  </si>
+  <si>
+    <t>LabelText("SER")</t>
+  </si>
+  <si>
+    <t>UTR</t>
+  </si>
+  <si>
+    <t>LabelText("UTR")</t>
   </si>
   <si>
     <t>UseWay</t>
@@ -124,7 +778,7 @@
     <t>使用方式</t>
   </si>
   <si>
-    <t>None</t>
+    <t>无</t>
   </si>
 </sst>
 </file>
@@ -141,7 +795,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -149,7 +803,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -157,14 +811,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +826,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -180,7 +834,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -188,7 +842,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,7 +850,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -204,14 +858,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -219,7 +873,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -227,7 +881,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -235,14 +889,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -250,42 +904,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -296,6 +950,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -467,12 +1127,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -484,12 +1138,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -616,7 +1285,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,109 +1297,109 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,9 +1409,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -796,221 +1483,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1020,9 +1493,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1036,40 +1509,40 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1102,9 +1575,9 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1132,40 +1605,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1179,38 +1678,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1269,153 +1750,1527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:L101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
+    <col min="4" max="5" width="14.1333333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.25" customWidth="1"/>
+    <col min="7" max="7" width="35.6333333333333" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="7.225" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.1333333333333" customWidth="1"/>
+    <col min="11" max="11" width="20.6333333333333" customWidth="1"/>
+    <col min="12" max="12" width="29.225" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="J3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4</v>
+      </c>
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:12">
+      <c r="H17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="2">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:12">
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="2">
+        <v>7</v>
+      </c>
+      <c r="K18" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:12">
+      <c r="H19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="2">
+        <v>8</v>
+      </c>
+      <c r="K19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:12">
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:12">
+      <c r="H21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:12">
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" s="2">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>71</v>
+      </c>
+      <c r="L22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:12">
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="2">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:12">
+      <c r="H24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="2">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:12">
+      <c r="H25" t="s">
+        <v>79</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" t="s">
+        <v>80</v>
+      </c>
+      <c r="L25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:12">
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26" s="2">
+        <v>6</v>
+      </c>
+      <c r="K26" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:12">
+      <c r="H27" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="2">
+        <v>7</v>
+      </c>
+      <c r="K27" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:12">
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s">
+        <v>89</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>90</v>
+      </c>
+      <c r="L28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:12">
+      <c r="H29" t="s">
+        <v>92</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>93</v>
+      </c>
+      <c r="L29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:12">
+      <c r="H30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="2">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>96</v>
+      </c>
+      <c r="L30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="2:12">
+      <c r="H31" t="s">
+        <v>60</v>
+      </c>
+      <c r="J31" s="2">
+        <v>3</v>
+      </c>
+      <c r="K31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="2:12">
+      <c r="H32" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" s="2">
+        <v>4</v>
+      </c>
+      <c r="K32" t="s">
+        <v>99</v>
+      </c>
+      <c r="L32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="2:12">
+      <c r="H33" t="s">
+        <v>101</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5</v>
+      </c>
+      <c r="K33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="2:12">
+      <c r="H34" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="2">
+        <v>6</v>
+      </c>
+      <c r="K34" t="s">
+        <v>105</v>
+      </c>
+      <c r="L34" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:12">
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" t="s">
+        <v>109</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="2:12">
+      <c r="H36" t="s">
+        <v>110</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="2:12">
+      <c r="H37" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="2:12">
+      <c r="H38" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="2:12">
+      <c r="H39" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:12">
+      <c r="H40" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="J40" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="2:12">
+      <c r="H41" t="s">
+        <v>114</v>
+      </c>
+      <c r="J41" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:12">
+      <c r="B42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>108</v>
+      </c>
+      <c r="H42" t="s">
+        <v>116</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0</v>
+      </c>
+      <c r="L42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:12">
+      <c r="H43" t="s">
+        <v>118</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:12">
+      <c r="H44" t="s">
+        <v>120</v>
+      </c>
+      <c r="J44" s="2">
+        <v>2</v>
+      </c>
+      <c r="L44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:12">
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>123</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:12">
+      <c r="H46" t="s">
+        <v>125</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="2:12">
+      <c r="H47" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47" s="2">
+        <v>2</v>
+      </c>
+      <c r="L47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="2:12">
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>130</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="2:12">
+      <c r="H49" t="s">
+        <v>132</v>
+      </c>
+      <c r="J49" s="2">
+        <v>1</v>
+      </c>
+      <c r="L49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="2:12">
+      <c r="H50" t="s">
+        <v>134</v>
+      </c>
+      <c r="J50" s="2">
+        <v>2</v>
+      </c>
+      <c r="L50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="2:12">
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>137</v>
+      </c>
+      <c r="J51" s="2">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="2:12">
+      <c r="H52" t="s">
+        <v>139</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="2:12">
+      <c r="H53" t="s">
+        <v>141</v>
+      </c>
+      <c r="J53" s="2">
+        <v>2</v>
+      </c>
+      <c r="L53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="2:12">
+      <c r="H54" t="s">
+        <v>143</v>
+      </c>
+      <c r="J54" s="2">
+        <v>3</v>
+      </c>
+      <c r="L54" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="2:12">
+      <c r="B55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>108</v>
+      </c>
+      <c r="H55" t="s">
+        <v>146</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="2:12">
+      <c r="H56" t="s">
+        <v>148</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="2:12">
+      <c r="H57" t="s">
+        <v>150</v>
+      </c>
+      <c r="J57" s="2">
+        <v>2</v>
+      </c>
+      <c r="L57" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="2:12">
+      <c r="H58" t="s">
+        <v>152</v>
+      </c>
+      <c r="J58" s="2">
+        <v>3</v>
+      </c>
+      <c r="L58" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>108</v>
+      </c>
+      <c r="H59" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="2:12">
+      <c r="H60" t="s">
+        <v>157</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="2:12">
+      <c r="H61" t="s">
+        <v>159</v>
+      </c>
+      <c r="J61" s="2">
+        <v>2</v>
+      </c>
+      <c r="L61" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="2:12">
+      <c r="H62" t="s">
+        <v>161</v>
+      </c>
+      <c r="J62" s="2">
+        <v>3</v>
+      </c>
+      <c r="L62" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="2:12">
+      <c r="B63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>164</v>
+      </c>
+      <c r="J63" s="2">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="2:12">
+      <c r="H64" t="s">
+        <v>166</v>
+      </c>
+      <c r="J64" s="2">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="2:12">
+      <c r="H65" t="s">
+        <v>168</v>
+      </c>
+      <c r="J65" s="2">
+        <v>2</v>
+      </c>
+      <c r="L65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="2:12">
+      <c r="H66" t="s">
+        <v>170</v>
+      </c>
+      <c r="J66" s="2">
+        <v>3</v>
+      </c>
+      <c r="L66" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="2:12">
+      <c r="B67" t="s">
+        <v>172</v>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="J67" s="2">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="2:12">
+      <c r="H68" t="s">
+        <v>174</v>
+      </c>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="2:12">
+      <c r="H69" t="s">
+        <v>176</v>
+      </c>
+      <c r="J69" s="2">
+        <v>2</v>
+      </c>
+      <c r="L69" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="2:12">
+      <c r="H70" t="s">
+        <v>178</v>
+      </c>
+      <c r="J70" s="2">
+        <v>3</v>
+      </c>
+      <c r="L70" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="2:12">
+      <c r="B71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>181</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="2:12">
+      <c r="H72" t="s">
+        <v>183</v>
+      </c>
+      <c r="J72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="2:12">
+      <c r="B73" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>186</v>
+      </c>
+      <c r="H73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="2:12">
+      <c r="H74" t="s">
         <v>22</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" t="s">
+      <c r="J74" s="2">
+        <v>1</v>
+      </c>
+      <c r="L74" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="2:12">
+      <c r="H75" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J75" s="2">
+        <v>2</v>
+      </c>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="2:12">
+      <c r="H76" t="s">
         <v>26</v>
       </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
+      <c r="J76" s="2">
+        <v>3</v>
+      </c>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="2:12">
+      <c r="H77" t="s">
+        <v>191</v>
+      </c>
+      <c r="J77" s="2">
+        <v>4</v>
+      </c>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="2:12">
+      <c r="B78" t="s">
+        <v>193</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>108</v>
+      </c>
+      <c r="H78" t="s">
+        <v>194</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="2:12">
+      <c r="H79" t="s">
+        <v>196</v>
+      </c>
+      <c r="J79" s="2">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="2:12">
+      <c r="H80" t="s">
+        <v>198</v>
+      </c>
+      <c r="J80" s="2">
+        <v>2</v>
+      </c>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="2:12">
+      <c r="B81" t="s">
+        <v>200</v>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>108</v>
+      </c>
+      <c r="H81" t="s">
+        <v>201</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="2:12">
+      <c r="H82" t="s">
+        <v>203</v>
+      </c>
+      <c r="J82" s="2">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="2:12">
+      <c r="B83" t="s">
+        <v>205</v>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>108</v>
+      </c>
+      <c r="H83" t="s">
+        <v>206</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B84" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>108</v>
+      </c>
+      <c r="H84" t="s">
+        <v>209</v>
+      </c>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="2:12">
+      <c r="H85" t="s">
+        <v>211</v>
+      </c>
+      <c r="J85" s="2">
+        <v>1</v>
+      </c>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="2:12">
+      <c r="H86" t="s">
+        <v>213</v>
+      </c>
+      <c r="J86" s="2">
+        <v>2</v>
+      </c>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="2:12">
+      <c r="H87" t="s">
+        <v>215</v>
+      </c>
+      <c r="J87" s="2">
+        <v>3</v>
+      </c>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="2:12">
+      <c r="B88" t="s">
+        <v>217</v>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>108</v>
+      </c>
+      <c r="H88" t="s">
+        <v>218</v>
+      </c>
+      <c r="J88" s="2">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="2:12">
+      <c r="H89" t="s">
+        <v>220</v>
+      </c>
+      <c r="J89" s="2">
+        <v>1</v>
+      </c>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B90" t="s">
+        <v>222</v>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>108</v>
+      </c>
+      <c r="H90" t="s">
+        <v>223</v>
+      </c>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" customHeight="1" spans="2:12">
+      <c r="H91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2">
+        <v>1</v>
+      </c>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="2:12">
+      <c r="H92" t="s">
+        <v>227</v>
+      </c>
+      <c r="J92" s="2">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="2:12">
+      <c r="H93" t="s">
+        <v>229</v>
+      </c>
+      <c r="J93" s="2">
+        <v>3</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="2:12">
+      <c r="H94" t="s">
+        <v>231</v>
+      </c>
+      <c r="J94" s="2">
+        <v>4</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="2:12">
+      <c r="B95" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>108</v>
+      </c>
+      <c r="H95" t="s">
+        <v>234</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="2:12">
+      <c r="H96" t="s">
+        <v>236</v>
+      </c>
+      <c r="J96" s="2">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="2:12">
+      <c r="H97" t="s">
+        <v>238</v>
+      </c>
+      <c r="J97" s="2">
+        <v>2</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="2:12">
+      <c r="H98" t="s">
+        <v>240</v>
+      </c>
+      <c r="J98" s="2">
+        <v>3</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="2:12">
+      <c r="H99" t="s">
+        <v>242</v>
+      </c>
+      <c r="J99" s="2">
+        <v>4</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="2:12">
+      <c r="H100" t="s">
+        <v>244</v>
+      </c>
+      <c r="J100" s="2">
+        <v>5</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="2:12">
+      <c r="B101" t="s">
+        <v>246</v>
+      </c>
+      <c r="C101" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>247</v>
+      </c>
+      <c r="H101" t="s">
+        <v>116</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/cfg/excel/__enums__.xlsx
+++ b/cfg/excel/__enums__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="31230" windowHeight="15135"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="248">
   <si>
     <t>##var</t>
   </si>
@@ -442,343 +442,340 @@
     <t>LabelText("连招")</t>
   </si>
   <si>
+    <t>VeryHigh</t>
+  </si>
+  <si>
+    <t>LabelText("超高伤害")</t>
+  </si>
+  <si>
+    <t>SkillType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>LabelText("普通技能")</t>
+  </si>
+  <si>
+    <t>SkillMove</t>
+  </si>
+  <si>
+    <t>LabelText("跑技能")</t>
+  </si>
+  <si>
+    <t>SkillJump</t>
+  </si>
+  <si>
+    <t>LabelText("跳技能")</t>
+  </si>
+  <si>
+    <t>SkillCharge</t>
+  </si>
+  <si>
+    <t>LabelText("充能技能")</t>
+  </si>
+  <si>
+    <t>SkillTurnType</t>
+  </si>
+  <si>
+    <t>TurnToMainTarget</t>
+  </si>
+  <si>
+    <t>LabelText("看向主目标")</t>
+  </si>
+  <si>
+    <t>FollowMainTarget</t>
+  </si>
+  <si>
+    <t>LabelText("跟随主目标")</t>
+  </si>
+  <si>
+    <t>TurnToSummoner</t>
+  </si>
+  <si>
+    <t>LabelText("看向主人")</t>
+  </si>
+  <si>
+    <t>FollowSummoner</t>
+  </si>
+  <si>
+    <t>LabelText("跟随主人")</t>
+  </si>
+  <si>
+    <t>MissileShootType</t>
+  </si>
+  <si>
+    <t>FindTarget</t>
+  </si>
+  <si>
+    <t>LabelText("索敌")</t>
+  </si>
+  <si>
+    <t>FindTargetAndBlock</t>
+  </si>
+  <si>
+    <t>LabelText("索敌并且碰撞")</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>LabelText("碰撞")</t>
+  </si>
+  <si>
+    <t>AlwaysBlock</t>
+  </si>
+  <si>
+    <t>LabelText("总是碰撞")</t>
+  </si>
+  <si>
+    <t>MissileType</t>
+  </si>
+  <si>
+    <t>LabelText("普通")</t>
+  </si>
+  <si>
+    <t>Catapult</t>
+  </si>
+  <si>
+    <t>LabelText("弹射")</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>LabelText("分裂")</t>
+  </si>
+  <si>
+    <t>SnapShoot</t>
+  </si>
+  <si>
+    <t>LabelText("闪射")</t>
+  </si>
+  <si>
+    <t>MoveType</t>
+  </si>
+  <si>
+    <t>BaseSpeed</t>
+  </si>
+  <si>
+    <t>LabelText("基于速度")</t>
+  </si>
+  <si>
+    <t>BaseTime</t>
+  </si>
+  <si>
+    <t>LabelText("基于时间")</t>
+  </si>
+  <si>
+    <t>HitType</t>
+  </si>
+  <si>
+    <t>Serializable, ActionName("受击类型")</t>
+  </si>
+  <si>
+    <t>LabelText("普通受击")</t>
+  </si>
+  <si>
+    <t>LabelText("击退")</t>
+  </si>
+  <si>
+    <t>LabelText("击倒")</t>
+  </si>
+  <si>
+    <t>LabelText("击飞")</t>
+  </si>
+  <si>
+    <t>HitStun</t>
+  </si>
+  <si>
+    <t>LabelText("击晕")</t>
+  </si>
+  <si>
+    <t>EntityType</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>LabelText("怪物")</t>
+  </si>
+  <si>
+    <t>Npc</t>
+  </si>
+  <si>
+    <t>LabelText("Npc")</t>
+  </si>
+  <si>
+    <t>AirWall</t>
+  </si>
+  <si>
+    <t>LabelText("空气墙")</t>
+  </si>
+  <si>
+    <t>RangeType</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>LabelText("圆形")</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>LabelText("矩形")</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>LabelText("剧情事件")</t>
+  </si>
+  <si>
+    <t>CollectionType</t>
+  </si>
+  <si>
+    <t>Ammo</t>
+  </si>
+  <si>
+    <t>LabelText("弹药")</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>LabelText("血包")</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>LabelText("护甲")</t>
+  </si>
+  <si>
+    <t>BodyArmor</t>
+  </si>
+  <si>
+    <t>LabelText("防弹衣")</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>LabelText("货币")</t>
+  </si>
+  <si>
+    <t>Prop</t>
+  </si>
+  <si>
+    <t>LabelText("道具")</t>
+  </si>
+  <si>
+    <t>JobType</t>
+  </si>
+  <si>
+    <t>BreakThrough</t>
+  </si>
+  <si>
+    <t>LabelText("突破")</t>
+  </si>
+  <si>
+    <t>Infantry</t>
+  </si>
+  <si>
+    <t>LabelText("步兵")</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>LabelText("重装")</t>
+  </si>
+  <si>
+    <t>Snip</t>
+  </si>
+  <si>
+    <t>LabelText("狙击")</t>
+  </si>
+  <si>
+    <t>Investigate</t>
+  </si>
+  <si>
+    <t>LabelText("侦查")</t>
+  </si>
+  <si>
+    <t>rarityType</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>LabelText("N")</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>LabelText("R")</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>LabelText("SR")</t>
+  </si>
+  <si>
+    <t>UR</t>
+  </si>
+  <si>
+    <t>LabelText("UR")</t>
+  </si>
+  <si>
+    <t>SER</t>
+  </si>
+  <si>
+    <t>LabelText("SER")</t>
+  </si>
+  <si>
+    <t>UTR</t>
+  </si>
+  <si>
+    <t>LabelText("UTR")</t>
+  </si>
+  <si>
+    <t>BattleType</t>
+  </si>
+  <si>
+    <t>PVE</t>
+  </si>
+  <si>
+    <t>LabelText("PVE")</t>
+  </si>
+  <si>
+    <t>PVP</t>
+  </si>
+  <si>
+    <t>LabelText("PVP")</t>
+  </si>
+  <si>
     <t>DamageType</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>LabelText("低伤害")</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>LabelText("中伤害")</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>LabelText("高伤害")</t>
-  </si>
-  <si>
-    <t>VeryHigh</t>
-  </si>
-  <si>
-    <t>LabelText("超高伤害")</t>
-  </si>
-  <si>
-    <t>SkillType</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>LabelText("普通技能")</t>
-  </si>
-  <si>
-    <t>SkillMove</t>
-  </si>
-  <si>
-    <t>LabelText("跑技能")</t>
-  </si>
-  <si>
-    <t>SkillJump</t>
-  </si>
-  <si>
-    <t>LabelText("跳技能")</t>
-  </si>
-  <si>
-    <t>SkillCharge</t>
-  </si>
-  <si>
-    <t>LabelText("充能技能")</t>
-  </si>
-  <si>
-    <t>SkillTurnType</t>
-  </si>
-  <si>
-    <t>TurnToMainTarget</t>
-  </si>
-  <si>
-    <t>LabelText("看向主目标")</t>
-  </si>
-  <si>
-    <t>FollowMainTarget</t>
-  </si>
-  <si>
-    <t>LabelText("跟随主目标")</t>
-  </si>
-  <si>
-    <t>TurnToSummoner</t>
-  </si>
-  <si>
-    <t>LabelText("看向主人")</t>
-  </si>
-  <si>
-    <t>FollowSummoner</t>
-  </si>
-  <si>
-    <t>LabelText("跟随主人")</t>
-  </si>
-  <si>
-    <t>MissileShootType</t>
-  </si>
-  <si>
-    <t>FindTarget</t>
-  </si>
-  <si>
-    <t>LabelText("索敌")</t>
-  </si>
-  <si>
-    <t>FindTargetAndBlock</t>
-  </si>
-  <si>
-    <t>LabelText("索敌并且碰撞")</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>LabelText("碰撞")</t>
-  </si>
-  <si>
-    <t>AlwaysBlock</t>
-  </si>
-  <si>
-    <t>LabelText("总是碰撞")</t>
-  </si>
-  <si>
-    <t>MissileType</t>
-  </si>
-  <si>
-    <t>LabelText("普通")</t>
-  </si>
-  <si>
-    <t>Catapult</t>
-  </si>
-  <si>
-    <t>LabelText("弹射")</t>
-  </si>
-  <si>
-    <t>Split</t>
-  </si>
-  <si>
-    <t>LabelText("分裂")</t>
-  </si>
-  <si>
-    <t>SnapShoot</t>
-  </si>
-  <si>
-    <t>LabelText("闪射")</t>
-  </si>
-  <si>
-    <t>MoveType</t>
-  </si>
-  <si>
-    <t>BaseSpeed</t>
-  </si>
-  <si>
-    <t>LabelText("基于速度")</t>
-  </si>
-  <si>
-    <t>BaseTime</t>
-  </si>
-  <si>
-    <t>LabelText("基于时间")</t>
-  </si>
-  <si>
-    <t>HitType</t>
-  </si>
-  <si>
-    <t>Serializable, ActionName("受击类型")</t>
-  </si>
-  <si>
-    <t>LabelText("普通受击")</t>
-  </si>
-  <si>
-    <t>LabelText("击退")</t>
-  </si>
-  <si>
-    <t>LabelText("击倒")</t>
-  </si>
-  <si>
-    <t>LabelText("击飞")</t>
-  </si>
-  <si>
-    <t>HitStun</t>
-  </si>
-  <si>
-    <t>LabelText("击晕")</t>
-  </si>
-  <si>
-    <t>EntityType</t>
-  </si>
-  <si>
-    <t>Monster</t>
-  </si>
-  <si>
-    <t>LabelText("怪物")</t>
-  </si>
-  <si>
-    <t>Npc</t>
-  </si>
-  <si>
-    <t>LabelText("Npc")</t>
-  </si>
-  <si>
-    <t>AirWall</t>
-  </si>
-  <si>
-    <t>LabelText("空气墙")</t>
-  </si>
-  <si>
-    <t>RangeType</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>LabelText("圆形")</t>
-  </si>
-  <si>
-    <t>Rectangle</t>
-  </si>
-  <si>
-    <t>LabelText("矩形")</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
-  </si>
-  <si>
-    <t>LabelText("剧情事件")</t>
-  </si>
-  <si>
-    <t>CollectionType</t>
-  </si>
-  <si>
-    <t>Ammo</t>
-  </si>
-  <si>
-    <t>LabelText("弹药")</t>
-  </si>
-  <si>
-    <t>Cure</t>
-  </si>
-  <si>
-    <t>LabelText("血包")</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>LabelText("护甲")</t>
-  </si>
-  <si>
-    <t>BodyArmor</t>
-  </si>
-  <si>
-    <t>LabelText("防弹衣")</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>LabelText("货币")</t>
-  </si>
-  <si>
-    <t>Prop</t>
-  </si>
-  <si>
-    <t>LabelText("道具")</t>
-  </si>
-  <si>
-    <t>JobType</t>
-  </si>
-  <si>
-    <t>BreakThrough</t>
-  </si>
-  <si>
-    <t>LabelText("突破")</t>
-  </si>
-  <si>
-    <t>Infantry</t>
-  </si>
-  <si>
-    <t>LabelText("步兵")</t>
-  </si>
-  <si>
-    <t>Tank</t>
-  </si>
-  <si>
-    <t>LabelText("重装")</t>
-  </si>
-  <si>
-    <t>Snip</t>
-  </si>
-  <si>
-    <t>LabelText("狙击")</t>
-  </si>
-  <si>
-    <t>Investigate</t>
-  </si>
-  <si>
-    <t>LabelText("侦查")</t>
-  </si>
-  <si>
-    <t>rarityType</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>LabelText("N")</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>LabelText("R")</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>LabelText("SR")</t>
-  </si>
-  <si>
-    <t>UR</t>
-  </si>
-  <si>
-    <t>LabelText("UR")</t>
-  </si>
-  <si>
-    <t>SER</t>
-  </si>
-  <si>
-    <t>LabelText("SER")</t>
-  </si>
-  <si>
-    <t>UTR</t>
-  </si>
-  <si>
-    <t>LabelText("UTR")</t>
-  </si>
-  <si>
-    <t>UseWay</t>
-  </si>
-  <si>
-    <t>使用方式</t>
-  </si>
-  <si>
-    <t>无</t>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>LabelText("属性伤害")</t>
+  </si>
+  <si>
+    <t>LabelText("普通伤害")</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1406,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1430,6 +1427,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2513,31 +2513,34 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:12">
-      <c r="B51" t="s">
+      <c r="H51" t="s">
         <v>136</v>
       </c>
-      <c r="C51" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="J51" s="2">
+        <v>3</v>
+      </c>
+      <c r="L51" t="s">
         <v>137</v>
       </c>
-      <c r="J51" s="2">
-        <v>0</v>
-      </c>
-      <c r="L51" t="s">
+    </row>
+    <row r="52" customHeight="1" spans="2:12">
+      <c r="B52" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="2:12">
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>108</v>
+      </c>
       <c r="H52" t="s">
         <v>139</v>
       </c>
       <c r="J52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="s">
         <v>140</v>
@@ -2548,7 +2551,7 @@
         <v>141</v>
       </c>
       <c r="J53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" t="s">
         <v>142</v>
@@ -2559,41 +2562,42 @@
         <v>143</v>
       </c>
       <c r="J54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:12">
-      <c r="B55" t="s">
+      <c r="H55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="J55" s="2">
+        <v>3</v>
+      </c>
+      <c r="L55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
         <v>108</v>
       </c>
-      <c r="H55" t="s">
-        <v>146</v>
-      </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="2:12">
       <c r="H56" t="s">
         <v>148</v>
       </c>
+      <c r="I56" s="2"/>
       <c r="J56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="s">
         <v>149</v>
@@ -2604,7 +2608,7 @@
         <v>150</v>
       </c>
       <c r="J57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" t="s">
         <v>151</v>
@@ -2615,42 +2619,38 @@
         <v>152</v>
       </c>
       <c r="J58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B59" t="s">
+    <row r="59" customHeight="1" spans="2:12">
+      <c r="H59" t="s">
         <v>154</v>
       </c>
-      <c r="C59" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" t="s">
-        <v>108</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="J59" s="2">
+        <v>3</v>
+      </c>
+      <c r="L59" t="s">
         <v>155</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
+    </row>
+    <row r="60" customHeight="1" spans="2:12">
+      <c r="B60" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="2:12">
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
       <c r="H60" t="s">
         <v>157</v>
       </c>
       <c r="J60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="s">
         <v>158</v>
@@ -2661,7 +2661,7 @@
         <v>159</v>
       </c>
       <c r="J61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" t="s">
         <v>160</v>
@@ -2672,91 +2672,91 @@
         <v>161</v>
       </c>
       <c r="J62" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
-      <c r="B63" t="s">
+      <c r="H63" t="s">
         <v>163</v>
       </c>
-      <c r="C63" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="J63" s="2">
+        <v>3</v>
+      </c>
+      <c r="L63" t="s">
         <v>164</v>
       </c>
-      <c r="J63" s="2">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
+    </row>
+    <row r="64" customHeight="1" spans="2:12">
+      <c r="B64" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="64" customHeight="1" spans="2:12">
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
       <c r="H64" t="s">
+        <v>29</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
         <v>166</v>
-      </c>
-      <c r="J64" s="2">
-        <v>1</v>
-      </c>
-      <c r="L64" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:12">
       <c r="H65" t="s">
+        <v>167</v>
+      </c>
+      <c r="J65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
         <v>168</v>
-      </c>
-      <c r="J65" s="2">
-        <v>2</v>
-      </c>
-      <c r="L65" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:12">
       <c r="H66" t="s">
+        <v>169</v>
+      </c>
+      <c r="J66" s="2">
+        <v>2</v>
+      </c>
+      <c r="L66" t="s">
         <v>170</v>
       </c>
-      <c r="J66" s="2">
+    </row>
+    <row r="67" customHeight="1" spans="2:12">
+      <c r="H67" t="s">
+        <v>171</v>
+      </c>
+      <c r="J67" s="2">
         <v>3</v>
       </c>
-      <c r="L66" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="2:12">
-      <c r="B67" t="s">
+      <c r="L67" t="s">
         <v>172</v>
       </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>29</v>
-      </c>
-      <c r="J67" s="2">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
+    </row>
+    <row r="68" customHeight="1" spans="2:12">
+      <c r="B68" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="2:12">
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
       <c r="H68" t="s">
         <v>174</v>
       </c>
       <c r="J68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="s">
         <v>175</v>
@@ -2767,106 +2767,112 @@
         <v>176</v>
       </c>
       <c r="J69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:12">
+      <c r="B70" t="s">
+        <v>178</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>179</v>
+      </c>
       <c r="H70" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="J70" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:12">
-      <c r="B71" t="s">
-        <v>180</v>
-      </c>
-      <c r="C71" t="b">
-        <v>0</v>
-      </c>
-      <c r="D71" t="b">
-        <v>1</v>
-      </c>
       <c r="H71" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
         <v>181</v>
-      </c>
-      <c r="J71" s="2">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:12">
       <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="2">
+        <v>2</v>
+      </c>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="2:12">
+      <c r="H73" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" s="2">
+        <v>3</v>
+      </c>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="J72" s="2">
-        <v>1</v>
-      </c>
-      <c r="L72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="2:12">
-      <c r="B73" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" t="b">
-        <v>0</v>
-      </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="G73" t="s">
-        <v>186</v>
-      </c>
-      <c r="H73" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="2">
-        <v>0</v>
-      </c>
-      <c r="L73" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:12">
       <c r="H74" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="J74" s="2">
-        <v>1</v>
-      </c>
-      <c r="L74" t="s">
-        <v>188</v>
+        <v>4</v>
+      </c>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:12">
+      <c r="B75" t="s">
+        <v>186</v>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>108</v>
+      </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="J75" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:12">
       <c r="H76" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="J76" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="2" t="s">
@@ -2878,7 +2884,7 @@
         <v>191</v>
       </c>
       <c r="J77" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K77" s="2"/>
       <c r="L77" s="2" t="s">
@@ -2922,20 +2928,32 @@
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:12">
+      <c r="B80" t="s">
+        <v>198</v>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>108</v>
+      </c>
       <c r="H80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J80" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="2:12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" customHeight="1" spans="2:12">
       <c r="B81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C81" t="b">
         <v>0</v>
@@ -2947,83 +2965,71 @@
         <v>108</v>
       </c>
       <c r="H81" t="s">
-        <v>201</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="I81" s="2"/>
       <c r="J81" s="2">
         <v>0</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:12">
       <c r="H82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J82" s="2">
         <v>1</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:12">
-      <c r="B83" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" t="b">
-        <v>0</v>
-      </c>
-      <c r="D83" t="b">
-        <v>1</v>
-      </c>
-      <c r="G83" t="s">
-        <v>108</v>
-      </c>
       <c r="H83" t="s">
         <v>206</v>
       </c>
       <c r="J83" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="84" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B84" t="s">
+    <row r="84" customHeight="1" spans="2:12">
+      <c r="H84" t="s">
         <v>208</v>
       </c>
-      <c r="C84" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="G84" t="s">
-        <v>108</v>
-      </c>
-      <c r="H84" t="s">
-        <v>209</v>
-      </c>
-      <c r="I84" s="2"/>
       <c r="J84" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="2:12">
+      <c r="B85" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="85" customHeight="1" spans="2:12">
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>108</v>
+      </c>
       <c r="H85" t="s">
         <v>211</v>
       </c>
       <c r="J85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2" t="s">
@@ -3035,43 +3041,45 @@
         <v>213</v>
       </c>
       <c r="J86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="2:12">
+    <row r="87" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B87" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>108</v>
+      </c>
       <c r="H87" t="s">
-        <v>215</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="I87" s="2"/>
       <c r="J87" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="2:12">
-      <c r="B88" t="s">
         <v>217</v>
       </c>
-      <c r="C88" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="G88" t="s">
-        <v>108</v>
-      </c>
+    </row>
+    <row r="88" customFormat="1" customHeight="1" spans="2:12">
       <c r="H88" t="s">
         <v>218</v>
       </c>
+      <c r="I88" s="2"/>
       <c r="J88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="2" t="s">
@@ -3083,57 +3091,52 @@
         <v>220</v>
       </c>
       <c r="J89" s="2">
-        <v>1</v>
-      </c>
-      <c r="K89" s="2"/>
+        <v>2</v>
+      </c>
       <c r="L89" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="90" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B90" t="s">
+    <row r="90" customHeight="1" spans="2:12">
+      <c r="H90" t="s">
         <v>222</v>
       </c>
-      <c r="C90" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="J90" s="2">
+        <v>3</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="2:12">
+      <c r="H91" t="s">
+        <v>224</v>
+      </c>
+      <c r="J91" s="2">
+        <v>4</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="2:12">
+      <c r="B92" t="s">
+        <v>226</v>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
         <v>108</v>
       </c>
-      <c r="H90" t="s">
-        <v>223</v>
-      </c>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2">
-        <v>0</v>
-      </c>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" customHeight="1" spans="2:12">
-      <c r="H91" t="s">
-        <v>225</v>
-      </c>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2">
-        <v>1</v>
-      </c>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="2:12">
       <c r="H92" t="s">
         <v>227</v>
       </c>
       <c r="J92" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>228</v>
@@ -3144,7 +3147,7 @@
         <v>229</v>
       </c>
       <c r="J93" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>230</v>
@@ -3155,63 +3158,64 @@
         <v>231</v>
       </c>
       <c r="J94" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:12">
-      <c r="B95" t="s">
+      <c r="H95" t="s">
         <v>233</v>
       </c>
-      <c r="C95" t="b">
-        <v>0</v>
-      </c>
-      <c r="D95" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" t="s">
-        <v>108</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="J95" s="2">
+        <v>3</v>
+      </c>
+      <c r="L95" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="J95" s="2">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:12">
       <c r="H96" t="s">
+        <v>235</v>
+      </c>
+      <c r="J96" s="2">
+        <v>4</v>
+      </c>
+      <c r="L96" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="J96" s="2">
-        <v>1</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="2:12">
       <c r="H97" t="s">
+        <v>237</v>
+      </c>
+      <c r="J97" s="2">
+        <v>5</v>
+      </c>
+      <c r="L97" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="J97" s="2">
-        <v>2</v>
-      </c>
-      <c r="L97" s="2" t="s">
+    </row>
+    <row r="98" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B98" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="98" customHeight="1" spans="2:12">
+      <c r="C98" t="b">
+        <v>0</v>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>108</v>
+      </c>
       <c r="H98" t="s">
         <v>240</v>
       </c>
+      <c r="I98" s="2"/>
       <c r="J98" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>241</v>
@@ -3222,47 +3226,45 @@
         <v>242</v>
       </c>
       <c r="J99" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="2:12">
+    <row r="100" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B100" t="s">
+        <v>244</v>
+      </c>
+      <c r="C100" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>108</v>
+      </c>
       <c r="H100" t="s">
-        <v>244</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I100" s="2"/>
       <c r="J100" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="2:12">
-      <c r="B101" t="s">
-        <v>246</v>
-      </c>
-      <c r="C101" t="b">
-        <v>0</v>
-      </c>
-      <c r="D101" t="b">
-        <v>1</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="H101" t="s">
+        <v>29</v>
+      </c>
+      <c r="J101" s="7">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
         <v>247</v>
-      </c>
-      <c r="H101" t="s">
-        <v>116</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101" t="s">
-        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/cfg/excel/__enums__.xlsx
+++ b/cfg/excel/__enums__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="16995"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="262">
   <si>
     <t>##var</t>
   </si>
@@ -662,6 +662,48 @@
   </si>
   <si>
     <t>LabelText("防弹衣")</t>
+  </si>
+  <si>
+    <t>Grip</t>
+  </si>
+  <si>
+    <t>LabelText("穿甲弹")</t>
+  </si>
+  <si>
+    <t>Handle</t>
+  </si>
+  <si>
+    <t>LabelText("握把")</t>
+  </si>
+  <si>
+    <t>Magazine</t>
+  </si>
+  <si>
+    <t>LabelText("弹夹")</t>
+  </si>
+  <si>
+    <t>Radar</t>
+  </si>
+  <si>
+    <t>LabelText("战术雷达")</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>LabelText("瞄准镜")</t>
+  </si>
+  <si>
+    <t>Shoe</t>
+  </si>
+  <si>
+    <t>LabelText("战术靴")</t>
+  </si>
+  <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>LabelText("消音器")</t>
   </si>
   <si>
     <t>ItemType</t>
@@ -1406,7 +1448,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1427,9 +1469,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1750,7 +1789,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -3013,258 +3052,352 @@
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:12">
-      <c r="B85" t="s">
+      <c r="H85" t="s">
         <v>210</v>
       </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
-      <c r="D85" t="b">
-        <v>1</v>
-      </c>
-      <c r="G85" t="s">
-        <v>108</v>
-      </c>
-      <c r="H85" t="s">
-        <v>211</v>
-      </c>
       <c r="J85" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:12">
       <c r="H86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J86" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="2:12">
+      <c r="H87" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="87" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B87" t="s">
-        <v>215</v>
-      </c>
-      <c r="C87" t="b">
-        <v>0</v>
-      </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="G87" t="s">
-        <v>108</v>
-      </c>
-      <c r="H87" t="s">
-        <v>216</v>
-      </c>
-      <c r="I87" s="2"/>
       <c r="J87" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" customHeight="1" spans="2:12">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="2:12">
       <c r="H88" t="s">
-        <v>218</v>
-      </c>
-      <c r="I88" s="2"/>
+        <v>216</v>
+      </c>
       <c r="J88" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:12">
       <c r="H89" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J89" s="2">
-        <v>2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K89" s="2"/>
       <c r="L89" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:12">
       <c r="H90" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J90" s="2">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K90" s="2"/>
       <c r="L90" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:12">
       <c r="H91" t="s">
+        <v>222</v>
+      </c>
+      <c r="J91" s="2">
+        <v>10</v>
+      </c>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="2:12">
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" customHeight="1" spans="2:12">
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" customHeight="1" spans="2:12">
+      <c r="B94" t="s">
         <v>224</v>
       </c>
-      <c r="J91" s="2">
-        <v>4</v>
-      </c>
-      <c r="L91" s="2" t="s">
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>108</v>
+      </c>
+      <c r="H94" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="92" customHeight="1" spans="2:12">
-      <c r="B92" t="s">
+      <c r="J94" s="2">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C92" t="b">
-        <v>0</v>
-      </c>
-      <c r="D92" t="b">
-        <v>1</v>
-      </c>
-      <c r="G92" t="s">
-        <v>108</v>
-      </c>
-      <c r="H92" t="s">
-        <v>227</v>
-      </c>
-      <c r="J92" s="2">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="2:12">
-      <c r="H93" t="s">
-        <v>229</v>
-      </c>
-      <c r="J93" s="2">
-        <v>1</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="2:12">
-      <c r="H94" t="s">
-        <v>231</v>
-      </c>
-      <c r="J94" s="2">
-        <v>2</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:12">
       <c r="H95" t="s">
+        <v>227</v>
+      </c>
+      <c r="J95" s="2">
+        <v>1</v>
+      </c>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>108</v>
+      </c>
+      <c r="H96" t="s">
+        <v>230</v>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" customHeight="1" spans="2:12">
+      <c r="H97" t="s">
+        <v>232</v>
+      </c>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2">
+        <v>1</v>
+      </c>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="J95" s="2">
-        <v>3</v>
-      </c>
-      <c r="L95" s="2" t="s">
+    </row>
+    <row r="98" customHeight="1" spans="2:12">
+      <c r="H98" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="96" customHeight="1" spans="2:12">
-      <c r="H96" t="s">
+      <c r="J98" s="2">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="J96" s="2">
-        <v>4</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="2:12">
-      <c r="H97" t="s">
-        <v>237</v>
-      </c>
-      <c r="J97" s="2">
-        <v>5</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="98" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B98" t="s">
-        <v>239</v>
-      </c>
-      <c r="C98" t="b">
-        <v>0</v>
-      </c>
-      <c r="D98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s">
-        <v>108</v>
-      </c>
-      <c r="H98" t="s">
-        <v>240</v>
-      </c>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="2:12">
       <c r="H99" t="s">
+        <v>236</v>
+      </c>
+      <c r="J99" s="2">
+        <v>3</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="2:12">
+      <c r="H100" t="s">
+        <v>238</v>
+      </c>
+      <c r="J100" s="2">
+        <v>4</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="2:12">
+      <c r="B101" t="s">
+        <v>240</v>
+      </c>
+      <c r="C101" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>108</v>
+      </c>
+      <c r="H101" t="s">
+        <v>241</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="J99" s="2">
-        <v>1</v>
-      </c>
-      <c r="L99" s="2" t="s">
+    </row>
+    <row r="102" customHeight="1" spans="2:12">
+      <c r="H102" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="100" customFormat="1" customHeight="1" spans="2:12">
-      <c r="B100" t="s">
+      <c r="J102" s="2">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C100" t="b">
-        <v>0</v>
-      </c>
-      <c r="D100" t="b">
-        <v>1</v>
-      </c>
-      <c r="G100" t="s">
+    </row>
+    <row r="103" customHeight="1" spans="2:12">
+      <c r="H103" t="s">
+        <v>245</v>
+      </c>
+      <c r="J103" s="2">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="2:12">
+      <c r="H104" t="s">
+        <v>247</v>
+      </c>
+      <c r="J104" s="2">
+        <v>3</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="2:12">
+      <c r="H105" t="s">
+        <v>249</v>
+      </c>
+      <c r="J105" s="2">
+        <v>4</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="2:12">
+      <c r="H106" t="s">
+        <v>251</v>
+      </c>
+      <c r="J106" s="2">
+        <v>5</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B107" t="s">
+        <v>253</v>
+      </c>
+      <c r="C107" t="b">
+        <v>0</v>
+      </c>
+      <c r="D107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
         <v>108</v>
       </c>
-      <c r="H100" t="s">
-        <v>245</v>
-      </c>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="2:12">
-      <c r="H101" t="s">
+      <c r="H107" t="s">
+        <v>254</v>
+      </c>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="2:12">
+      <c r="H108" t="s">
+        <v>256</v>
+      </c>
+      <c r="J108" s="2">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B109" t="s">
+        <v>258</v>
+      </c>
+      <c r="C109" t="b">
+        <v>0</v>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>108</v>
+      </c>
+      <c r="H109" t="s">
+        <v>259</v>
+      </c>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="2:12">
+      <c r="H110" t="s">
         <v>29</v>
       </c>
-      <c r="J101" s="7">
-        <v>1</v>
-      </c>
-      <c r="L101" t="s">
-        <v>247</v>
+      <c r="J110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/cfg/excel/__enums__.xlsx
+++ b/cfg/excel/__enums__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16995"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="274">
   <si>
     <t>##var</t>
   </si>
@@ -818,6 +818,42 @@
   </si>
   <si>
     <t>LabelText("普通伤害")</t>
+  </si>
+  <si>
+    <t>AssetType</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>LabelText("物品")</t>
+  </si>
+  <si>
+    <t>Equip</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>LabelText("装备")</t>
+  </si>
+  <si>
+    <t>英雄</t>
+  </si>
+  <si>
+    <t>LabelText("英雄")</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>LabelText("武器")</t>
   </si>
 </sst>
 </file>
@@ -1789,7 +1825,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -3400,6 +3436,74 @@
         <v>261</v>
       </c>
     </row>
+    <row r="111" customHeight="1" spans="2:12">
+      <c r="B111" t="s">
+        <v>262</v>
+      </c>
+      <c r="C111" t="b">
+        <v>0</v>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>108</v>
+      </c>
+      <c r="H111" t="s">
+        <v>263</v>
+      </c>
+      <c r="J111" s="2">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="2:12">
+      <c r="H112" t="s">
+        <v>266</v>
+      </c>
+      <c r="J112" s="2">
+        <v>2</v>
+      </c>
+      <c r="K112" t="s">
+        <v>267</v>
+      </c>
+      <c r="L112" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="8:12">
+      <c r="H113" t="s">
+        <v>101</v>
+      </c>
+      <c r="J113" s="2">
+        <v>3</v>
+      </c>
+      <c r="K113" t="s">
+        <v>269</v>
+      </c>
+      <c r="L113" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="8:12">
+      <c r="H114" t="s">
+        <v>271</v>
+      </c>
+      <c r="J114" s="2">
+        <v>4</v>
+      </c>
+      <c r="K114" t="s">
+        <v>272</v>
+      </c>
+      <c r="L114" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
